--- a/examples/gen_zhixin.xlsx
+++ b/examples/gen_zhixin.xlsx
@@ -660,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -730,6 +730,13 @@
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
+    </border>
+    <border diagonalUp="1">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="thin"/>
     </border>
     <border>
       <left/>
@@ -951,10 +958,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -964,49 +971,49 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -1016,27 +1023,27 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="30" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">

--- a/examples/gen_zhixin.xlsx
+++ b/examples/gen_zhixin.xlsx
@@ -882,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -975,7 +975,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
@@ -1007,11 +1010,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1335,15 +1344,15 @@
       <c r="A6" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="32" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="36" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="32" t="s">
@@ -1352,34 +1361,34 @@
       <c r="H6" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="32" t="s">
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="36" t="s">
         <v>29</v>
       </c>
       <c r="O6" s="27"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="32" t="s">
+      <c r="P6" s="37"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="36" t="s">
         <v>30</v>
       </c>
       <c r="T6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="U6" s="32" t="s">
+      <c r="U6" s="36" t="s">
         <v>32</v>
       </c>
       <c r="V6" s="27"/>
       <c r="W6" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="X6" s="38"/>
+      <c r="X6" s="39"/>
       <c r="Y6" s="32" t="s">
         <v>34</v>
       </c>
@@ -1407,107 +1416,107 @@
       <c r="AI6" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="AJ6" s="39"/>
+      <c r="AJ6" s="40"/>
     </row>
     <row r="7" ht="9.00" customHeight="1">
       <c r="A7" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="41" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="30"/>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40" t="s">
+      <c r="G7" s="41"/>
+      <c r="H7" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="40"/>
+      <c r="I7" s="41"/>
       <c r="J7" s="30"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
       <c r="O7" s="30"/>
-      <c r="P7" s="40" t="s">
+      <c r="P7" s="41" t="s">
         <v>48</v>
       </c>
       <c r="Q7" s="30"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
       <c r="V7" s="30"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
       <c r="Z7" s="30"/>
-      <c r="AA7" s="40"/>
+      <c r="AA7" s="41"/>
       <c r="AB7" s="30"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="42"/>
+      <c r="AE7" s="42"/>
+      <c r="AF7" s="42"/>
       <c r="AG7" s="30"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="42"/>
+      <c r="AH7" s="42"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="43"/>
     </row>
     <row r="8" ht="9.00" customHeight="1">
-      <c r="A8" s="43"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="44" t="s">
+      <c r="A8" s="44"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="AE8" s="44" t="s">
+      <c r="AE8" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="AF8" s="44" t="s">
+      <c r="AF8" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="AG8" s="45"/>
-      <c r="AH8" s="44" t="s">
+      <c r="AG8" s="46"/>
+      <c r="AH8" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="AI8" s="44" t="s">
+      <c r="AI8" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="AJ8" s="46" t="s">
+      <c r="AJ8" s="47" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1515,117 +1524,117 @@
       <c r="A9" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="41" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="30"/>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40" t="s">
+      <c r="G9" s="41"/>
+      <c r="H9" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="41" t="s">
         <v>56</v>
       </c>
       <c r="J9" s="30"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
       <c r="O9" s="30"/>
-      <c r="P9" s="40" t="s">
+      <c r="P9" s="41" t="s">
         <v>57</v>
       </c>
       <c r="Q9" s="30"/>
-      <c r="R9" s="40" t="s">
+      <c r="R9" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="S9" s="40">
+      <c r="S9" s="41">
         <v>0.6</v>
       </c>
-      <c r="T9" s="40" t="s">
+      <c r="T9" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="U9" s="40" t="s">
+      <c r="U9" s="41" t="s">
         <v>60</v>
       </c>
       <c r="V9" s="30"/>
-      <c r="W9" s="40" t="s">
+      <c r="W9" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="40" t="s">
+      <c r="X9" s="41"/>
+      <c r="Y9" s="41" t="s">
         <v>62</v>
       </c>
       <c r="Z9" s="30"/>
-      <c r="AA9" s="40"/>
+      <c r="AA9" s="41"/>
       <c r="AB9" s="30"/>
-      <c r="AC9" s="40" t="s">
+      <c r="AC9" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="38"/>
-      <c r="AJ9" s="39"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="39"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="40"/>
     </row>
     <row r="10" ht="9.00" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="36"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="38"/>
-      <c r="AD10" s="40" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="AE10" s="40" t="s">
+      <c r="AE10" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="AF10" s="40" t="s">
+      <c r="AF10" s="41" t="s">
         <v>65</v>
       </c>
       <c r="AG10" s="30"/>
-      <c r="AH10" s="40" t="s">
+      <c r="AH10" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="AI10" s="40" t="s">
+      <c r="AI10" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="AJ10" s="47" t="s">
+      <c r="AJ10" s="48" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1633,117 +1642,117 @@
       <c r="A11" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="30"/>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40" t="s">
+      <c r="G11" s="41"/>
+      <c r="H11" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="41" t="s">
         <v>72</v>
       </c>
       <c r="J11" s="30"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
       <c r="O11" s="30"/>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="41" t="s">
         <v>73</v>
       </c>
       <c r="Q11" s="30"/>
-      <c r="R11" s="40" t="s">
+      <c r="R11" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="S11" s="40">
+      <c r="S11" s="41">
         <v>0.6</v>
       </c>
-      <c r="T11" s="40" t="s">
+      <c r="T11" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="U11" s="40" t="s">
+      <c r="U11" s="41" t="s">
         <v>60</v>
       </c>
       <c r="V11" s="30"/>
-      <c r="W11" s="40" t="s">
+      <c r="W11" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40" t="s">
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41" t="s">
         <v>74</v>
       </c>
       <c r="Z11" s="30"/>
-      <c r="AA11" s="40"/>
+      <c r="AA11" s="41"/>
       <c r="AB11" s="30"/>
-      <c r="AC11" s="40" t="s">
+      <c r="AC11" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="AD11" s="38"/>
-      <c r="AE11" s="38"/>
-      <c r="AF11" s="36"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="38"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="39"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="39"/>
+      <c r="AF11" s="37"/>
+      <c r="AG11" s="38"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="40"/>
     </row>
     <row r="12" ht="9.00" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="40" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="AE12" s="40" t="s">
+      <c r="AE12" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="AF12" s="40" t="s">
+      <c r="AF12" s="41" t="s">
         <v>65</v>
       </c>
       <c r="AG12" s="30"/>
-      <c r="AH12" s="40" t="s">
+      <c r="AH12" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="AI12" s="40" t="s">
+      <c r="AI12" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="AJ12" s="47" t="s">
+      <c r="AJ12" s="48" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1751,117 +1760,117 @@
       <c r="A13" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="41" t="s">
         <v>80</v>
       </c>
       <c r="D13" s="30"/>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40" t="s">
+      <c r="G13" s="41"/>
+      <c r="H13" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="41" t="s">
         <v>83</v>
       </c>
       <c r="J13" s="30"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
       <c r="O13" s="30"/>
-      <c r="P13" s="40" t="s">
+      <c r="P13" s="41" t="s">
         <v>84</v>
       </c>
       <c r="Q13" s="30"/>
-      <c r="R13" s="40" t="s">
+      <c r="R13" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="S13" s="40">
+      <c r="S13" s="41">
         <v>0.6</v>
       </c>
-      <c r="T13" s="40" t="s">
+      <c r="T13" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="U13" s="40" t="s">
+      <c r="U13" s="41" t="s">
         <v>60</v>
       </c>
       <c r="V13" s="30"/>
-      <c r="W13" s="40" t="s">
+      <c r="W13" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40" t="s">
+      <c r="X13" s="41"/>
+      <c r="Y13" s="41" t="s">
         <v>85</v>
       </c>
       <c r="Z13" s="30"/>
-      <c r="AA13" s="40"/>
+      <c r="AA13" s="41"/>
       <c r="AB13" s="30"/>
-      <c r="AC13" s="40" t="s">
+      <c r="AC13" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="AD13" s="38"/>
-      <c r="AE13" s="38"/>
-      <c r="AF13" s="36"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="38"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="37"/>
+      <c r="AG13" s="38"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="40"/>
     </row>
     <row r="14" ht="9.00" customHeight="1">
-      <c r="A14" s="43"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="38"/>
-      <c r="AD14" s="40" t="s">
+      <c r="A14" s="44"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="37"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="37"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="AE14" s="40" t="s">
+      <c r="AE14" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="AF14" s="40" t="s">
+      <c r="AF14" s="41" t="s">
         <v>65</v>
       </c>
       <c r="AG14" s="30"/>
-      <c r="AH14" s="40" t="s">
+      <c r="AH14" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="AI14" s="40" t="s">
+      <c r="AI14" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="AJ14" s="47" t="s">
+      <c r="AJ14" s="48" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1869,117 +1878,117 @@
       <c r="A15" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>91</v>
       </c>
       <c r="D15" s="30"/>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40" t="s">
+      <c r="G15" s="41"/>
+      <c r="H15" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="41" t="s">
         <v>94</v>
       </c>
       <c r="J15" s="30"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
       <c r="O15" s="30"/>
-      <c r="P15" s="40" t="s">
+      <c r="P15" s="41" t="s">
         <v>95</v>
       </c>
       <c r="Q15" s="30"/>
-      <c r="R15" s="40" t="s">
+      <c r="R15" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="S15" s="40">
+      <c r="S15" s="41">
         <v>0.6</v>
       </c>
-      <c r="T15" s="40" t="s">
+      <c r="T15" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="U15" s="40" t="s">
+      <c r="U15" s="41" t="s">
         <v>60</v>
       </c>
       <c r="V15" s="30"/>
-      <c r="W15" s="40" t="s">
+      <c r="W15" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="40" t="s">
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41" t="s">
         <v>72</v>
       </c>
       <c r="Z15" s="30"/>
-      <c r="AA15" s="40"/>
+      <c r="AA15" s="41"/>
       <c r="AB15" s="30"/>
-      <c r="AC15" s="40" t="s">
+      <c r="AC15" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="AD15" s="38"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="36"/>
-      <c r="AG15" s="37"/>
-      <c r="AH15" s="38"/>
-      <c r="AI15" s="38"/>
-      <c r="AJ15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="37"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="40"/>
     </row>
     <row r="16" ht="9.00" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="38"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="36"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="38"/>
-      <c r="AD16" s="40" t="s">
+      <c r="A16" s="44"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="39"/>
+      <c r="X16" s="39"/>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="38"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="AE16" s="40" t="s">
+      <c r="AE16" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="AF16" s="40" t="s">
+      <c r="AF16" s="41" t="s">
         <v>65</v>
       </c>
       <c r="AG16" s="30"/>
-      <c r="AH16" s="40" t="s">
+      <c r="AH16" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AI16" s="40" t="s">
+      <c r="AI16" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AJ16" s="47" t="s">
+      <c r="AJ16" s="48" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1987,117 +1996,117 @@
       <c r="A17" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>101</v>
       </c>
       <c r="D17" s="30"/>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40" t="s">
+      <c r="G17" s="41"/>
+      <c r="H17" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="41" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="30"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
       <c r="O17" s="30"/>
-      <c r="P17" s="40" t="s">
+      <c r="P17" s="41" t="s">
         <v>105</v>
       </c>
       <c r="Q17" s="30"/>
-      <c r="R17" s="40" t="s">
+      <c r="R17" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="S17" s="40">
+      <c r="S17" s="41">
         <v>0.6</v>
       </c>
-      <c r="T17" s="40" t="s">
+      <c r="T17" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="U17" s="40" t="s">
+      <c r="U17" s="41" t="s">
         <v>60</v>
       </c>
       <c r="V17" s="30"/>
-      <c r="W17" s="40" t="s">
+      <c r="W17" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="40" t="s">
+      <c r="X17" s="41"/>
+      <c r="Y17" s="41" t="s">
         <v>87</v>
       </c>
       <c r="Z17" s="30"/>
-      <c r="AA17" s="40"/>
+      <c r="AA17" s="41"/>
       <c r="AB17" s="30"/>
-      <c r="AC17" s="40" t="s">
+      <c r="AC17" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="AD17" s="38"/>
-      <c r="AE17" s="38"/>
-      <c r="AF17" s="36"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="38"/>
-      <c r="AI17" s="38"/>
-      <c r="AJ17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="39"/>
+      <c r="AF17" s="37"/>
+      <c r="AG17" s="38"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
+      <c r="AJ17" s="40"/>
     </row>
     <row r="18" ht="9.00" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="38"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="38"/>
-      <c r="AD18" s="40" t="s">
+      <c r="A18" s="44"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="38"/>
+      <c r="AA18" s="37"/>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="39"/>
+      <c r="AD18" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="AE18" s="40" t="s">
+      <c r="AE18" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="AF18" s="40" t="s">
+      <c r="AF18" s="41" t="s">
         <v>107</v>
       </c>
       <c r="AG18" s="30"/>
-      <c r="AH18" s="40" t="s">
+      <c r="AH18" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="AI18" s="40" t="s">
+      <c r="AI18" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="AJ18" s="47" t="s">
+      <c r="AJ18" s="48" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2105,555 +2114,555 @@
       <c r="A19" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="41" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="30"/>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40" t="s">
+      <c r="G19" s="41"/>
+      <c r="H19" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="40"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="30"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
       <c r="O19" s="30"/>
-      <c r="P19" s="40" t="s">
+      <c r="P19" s="41" t="s">
         <v>48</v>
       </c>
       <c r="Q19" s="30"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
       <c r="V19" s="30"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="40"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41"/>
       <c r="Z19" s="30"/>
-      <c r="AA19" s="40"/>
+      <c r="AA19" s="41"/>
       <c r="AB19" s="30"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="38"/>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="36"/>
-      <c r="AG19" s="37"/>
-      <c r="AH19" s="38"/>
-      <c r="AI19" s="38"/>
-      <c r="AJ19" s="39"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="39"/>
+      <c r="AE19" s="39"/>
+      <c r="AF19" s="37"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="40"/>
     </row>
     <row r="20" ht="9.00" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="36"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="40"/>
-      <c r="AE20" s="40"/>
-      <c r="AF20" s="40"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="37"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="37"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
       <c r="AG20" s="30"/>
-      <c r="AH20" s="40"/>
-      <c r="AI20" s="40"/>
-      <c r="AJ20" s="47"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="48"/>
     </row>
     <row r="21" ht="9.00" customHeight="1">
       <c r="A21" s="25"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="30"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="30"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
       <c r="O21" s="30"/>
-      <c r="P21" s="40"/>
+      <c r="P21" s="41"/>
       <c r="Q21" s="30"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="40"/>
-      <c r="U21" s="40"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="41"/>
       <c r="V21" s="30"/>
-      <c r="W21" s="40"/>
-      <c r="X21" s="40"/>
-      <c r="Y21" s="40"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
       <c r="Z21" s="30"/>
-      <c r="AA21" s="40"/>
+      <c r="AA21" s="41"/>
       <c r="AB21" s="30"/>
-      <c r="AC21" s="40"/>
-      <c r="AD21" s="38"/>
-      <c r="AE21" s="38"/>
-      <c r="AF21" s="36"/>
-      <c r="AG21" s="37"/>
-      <c r="AH21" s="38"/>
-      <c r="AI21" s="38"/>
-      <c r="AJ21" s="39"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="39"/>
+      <c r="AE21" s="39"/>
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="38"/>
+      <c r="AH21" s="39"/>
+      <c r="AI21" s="39"/>
+      <c r="AJ21" s="40"/>
     </row>
     <row r="22" ht="9.00" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="37"/>
-      <c r="W22" s="38"/>
-      <c r="X22" s="38"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="37"/>
-      <c r="AA22" s="36"/>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="38"/>
-      <c r="AD22" s="40"/>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="40"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="38"/>
+      <c r="AA22" s="37"/>
+      <c r="AB22" s="38"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
       <c r="AG22" s="30"/>
-      <c r="AH22" s="40"/>
-      <c r="AI22" s="40"/>
-      <c r="AJ22" s="47"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="48"/>
     </row>
     <row r="23" ht="9.00" customHeight="1">
       <c r="A23" s="25"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="30"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="30"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
       <c r="O23" s="30"/>
-      <c r="P23" s="40"/>
+      <c r="P23" s="41"/>
       <c r="Q23" s="30"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="40"/>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+      <c r="U23" s="41"/>
       <c r="V23" s="30"/>
-      <c r="W23" s="40"/>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="40"/>
+      <c r="W23" s="41"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="41"/>
       <c r="Z23" s="30"/>
-      <c r="AA23" s="40"/>
+      <c r="AA23" s="41"/>
       <c r="AB23" s="30"/>
-      <c r="AC23" s="40"/>
-      <c r="AD23" s="38"/>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="36"/>
-      <c r="AG23" s="37"/>
-      <c r="AH23" s="38"/>
-      <c r="AI23" s="38"/>
-      <c r="AJ23" s="39"/>
+      <c r="AC23" s="41"/>
+      <c r="AD23" s="39"/>
+      <c r="AE23" s="39"/>
+      <c r="AF23" s="37"/>
+      <c r="AG23" s="38"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="39"/>
+      <c r="AJ23" s="40"/>
     </row>
     <row r="24" ht="9.00" customHeight="1">
-      <c r="A24" s="43"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="37"/>
-      <c r="R24" s="38"/>
-      <c r="S24" s="38"/>
-      <c r="T24" s="38"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="37"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="38"/>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="37"/>
-      <c r="AA24" s="36"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="38"/>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="40"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="39"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="38"/>
+      <c r="AA24" s="37"/>
+      <c r="AB24" s="38"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="41"/>
+      <c r="AE24" s="41"/>
+      <c r="AF24" s="41"/>
       <c r="AG24" s="30"/>
-      <c r="AH24" s="40"/>
-      <c r="AI24" s="40"/>
-      <c r="AJ24" s="47"/>
+      <c r="AH24" s="41"/>
+      <c r="AI24" s="41"/>
+      <c r="AJ24" s="48"/>
     </row>
     <row r="25" ht="9.00" customHeight="1">
       <c r="A25" s="25"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="30"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
       <c r="J25" s="30"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
       <c r="O25" s="30"/>
-      <c r="P25" s="40"/>
+      <c r="P25" s="41"/>
       <c r="Q25" s="30"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="40"/>
-      <c r="T25" s="40"/>
-      <c r="U25" s="40"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+      <c r="U25" s="41"/>
       <c r="V25" s="30"/>
-      <c r="W25" s="40"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40"/>
+      <c r="W25" s="41"/>
+      <c r="X25" s="41"/>
+      <c r="Y25" s="41"/>
       <c r="Z25" s="30"/>
-      <c r="AA25" s="40"/>
+      <c r="AA25" s="41"/>
       <c r="AB25" s="30"/>
-      <c r="AC25" s="40"/>
-      <c r="AD25" s="38"/>
-      <c r="AE25" s="38"/>
-      <c r="AF25" s="36"/>
-      <c r="AG25" s="37"/>
-      <c r="AH25" s="38"/>
-      <c r="AI25" s="38"/>
-      <c r="AJ25" s="39"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="39"/>
+      <c r="AF25" s="37"/>
+      <c r="AG25" s="38"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="39"/>
+      <c r="AJ25" s="40"/>
     </row>
     <row r="26" ht="9.00" customHeight="1">
-      <c r="A26" s="43"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="38"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="38"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="38"/>
-      <c r="X26" s="38"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="36"/>
-      <c r="AB26" s="37"/>
-      <c r="AC26" s="38"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="40"/>
-      <c r="AF26" s="40"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="37"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="41"/>
+      <c r="AE26" s="41"/>
+      <c r="AF26" s="41"/>
       <c r="AG26" s="30"/>
-      <c r="AH26" s="40"/>
-      <c r="AI26" s="40"/>
-      <c r="AJ26" s="47"/>
+      <c r="AH26" s="41"/>
+      <c r="AI26" s="41"/>
+      <c r="AJ26" s="48"/>
     </row>
     <row r="27" ht="9.00" customHeight="1">
       <c r="A27" s="25"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
       <c r="D27" s="30"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="30"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
       <c r="O27" s="30"/>
-      <c r="P27" s="40"/>
+      <c r="P27" s="41"/>
       <c r="Q27" s="30"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="40"/>
-      <c r="U27" s="40"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
       <c r="V27" s="30"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
       <c r="Z27" s="30"/>
-      <c r="AA27" s="40"/>
+      <c r="AA27" s="41"/>
       <c r="AB27" s="30"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="38"/>
-      <c r="AE27" s="38"/>
-      <c r="AF27" s="36"/>
-      <c r="AG27" s="37"/>
-      <c r="AH27" s="38"/>
-      <c r="AI27" s="38"/>
-      <c r="AJ27" s="39"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="39"/>
+      <c r="AE27" s="39"/>
+      <c r="AF27" s="37"/>
+      <c r="AG27" s="38"/>
+      <c r="AH27" s="39"/>
+      <c r="AI27" s="39"/>
+      <c r="AJ27" s="40"/>
     </row>
     <row r="28" ht="9.00" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="36"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="36"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="38"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="36"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="38"/>
-      <c r="AD28" s="40"/>
-      <c r="AE28" s="40"/>
-      <c r="AF28" s="40"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="38"/>
+      <c r="AA28" s="37"/>
+      <c r="AB28" s="38"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
       <c r="AG28" s="30"/>
-      <c r="AH28" s="40"/>
-      <c r="AI28" s="40"/>
-      <c r="AJ28" s="48"/>
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="49"/>
     </row>
     <row r="29" ht="9.00" customHeight="1">
       <c r="A29" s="25"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="30"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
       <c r="J29" s="30"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
       <c r="O29" s="30"/>
-      <c r="P29" s="40"/>
+      <c r="P29" s="41"/>
       <c r="Q29" s="30"/>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="40"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
       <c r="V29" s="30"/>
-      <c r="W29" s="40"/>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
       <c r="Z29" s="30"/>
-      <c r="AA29" s="40"/>
+      <c r="AA29" s="41"/>
       <c r="AB29" s="30"/>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="38"/>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="36"/>
-      <c r="AG29" s="37"/>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="38"/>
-      <c r="AJ29" s="48"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="39"/>
+      <c r="AF29" s="37"/>
+      <c r="AG29" s="38"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="49"/>
     </row>
     <row r="30" ht="9.00" customHeight="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="37"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="37"/>
-      <c r="W30" s="38"/>
-      <c r="X30" s="38"/>
-      <c r="Y30" s="36"/>
-      <c r="Z30" s="37"/>
-      <c r="AA30" s="36"/>
-      <c r="AB30" s="37"/>
-      <c r="AC30" s="38"/>
-      <c r="AD30" s="41"/>
-      <c r="AE30" s="41"/>
-      <c r="AF30" s="41"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="38"/>
+      <c r="AA30" s="37"/>
+      <c r="AB30" s="38"/>
+      <c r="AC30" s="39"/>
+      <c r="AD30" s="42"/>
+      <c r="AE30" s="42"/>
+      <c r="AF30" s="42"/>
       <c r="AG30" s="30"/>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="41"/>
-      <c r="AJ30" s="42"/>
+      <c r="AH30" s="42"/>
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="43"/>
     </row>
     <row r="31" ht="9.00" customHeight="1">
       <c r="A31" s="25"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="30"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
       <c r="J31" s="30"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
       <c r="O31" s="30"/>
-      <c r="P31" s="40"/>
+      <c r="P31" s="41"/>
       <c r="Q31" s="30"/>
-      <c r="R31" s="40"/>
-      <c r="S31" s="40"/>
-      <c r="T31" s="40"/>
-      <c r="U31" s="40"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
       <c r="V31" s="30"/>
-      <c r="W31" s="40"/>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="40"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
       <c r="Z31" s="30"/>
-      <c r="AA31" s="40"/>
+      <c r="AA31" s="41"/>
       <c r="AB31" s="30"/>
-      <c r="AC31" s="40"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="50"/>
-      <c r="AG31" s="45"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="51"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="50"/>
+      <c r="AE31" s="50"/>
+      <c r="AF31" s="51"/>
+      <c r="AG31" s="46"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="52"/>
     </row>
     <row r="32" ht="9.00" customHeight="1">
-      <c r="A32" s="43"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="37"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="38"/>
-      <c r="T32" s="38"/>
-      <c r="U32" s="36"/>
-      <c r="V32" s="37"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="38"/>
-      <c r="Y32" s="36"/>
-      <c r="Z32" s="37"/>
-      <c r="AA32" s="36"/>
-      <c r="AB32" s="37"/>
-      <c r="AC32" s="38"/>
-      <c r="AD32" s="44"/>
-      <c r="AE32" s="44"/>
-      <c r="AF32" s="44"/>
-      <c r="AG32" s="37"/>
-      <c r="AH32" s="44"/>
-      <c r="AI32" s="44"/>
-      <c r="AJ32" s="46"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="39"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="37"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="39"/>
+      <c r="X32" s="39"/>
+      <c r="Y32" s="37"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="37"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="39"/>
+      <c r="AD32" s="45"/>
+      <c r="AE32" s="45"/>
+      <c r="AF32" s="45"/>
+      <c r="AG32" s="38"/>
+      <c r="AH32" s="45"/>
+      <c r="AI32" s="45"/>
+      <c r="AJ32" s="47"/>
     </row>
     <row r="33" ht="15.00" customHeight="1">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="53" t="s">
         <v>114</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="27"/>
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="54" t="s">
         <v>115</v>
       </c>
       <c r="E33" s="26"/>
@@ -2663,7 +2672,7 @@
         <v>116</v>
       </c>
       <c r="I33" s="27"/>
-      <c r="J33" s="52" t="s">
+      <c r="J33" s="54" t="s">
         <v>117</v>
       </c>
       <c r="K33" s="26"/>
@@ -2672,18 +2681,18 @@
         <v>118</v>
       </c>
       <c r="N33" s="27"/>
-      <c r="O33" s="53"/>
+      <c r="O33" s="55"/>
       <c r="P33" s="26"/>
       <c r="Q33" s="32" t="s">
         <v>119</v>
       </c>
       <c r="R33" s="27"/>
-      <c r="S33" s="52" t="s">
+      <c r="S33" s="54" t="s">
         <v>120</v>
       </c>
       <c r="T33" s="26"/>
       <c r="U33" s="27"/>
-      <c r="V33" s="40" t="s">
+      <c r="V33" s="56" t="s">
         <v>121</v>
       </c>
       <c r="W33" s="32" t="s">
@@ -2707,17 +2716,17 @@
       </c>
       <c r="AH33" s="26"/>
       <c r="AI33" s="27"/>
-      <c r="AJ33" s="54" t="s">
+      <c r="AJ33" s="57" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" ht="15.00" customHeight="1">
-      <c r="A34" s="35" t="s">
+      <c r="A34" s="53" t="s">
         <v>126</v>
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="27"/>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="54" t="s">
         <v>127</v>
       </c>
       <c r="E34" s="26"/>
@@ -2727,7 +2736,7 @@
         <v>128</v>
       </c>
       <c r="I34" s="27"/>
-      <c r="J34" s="52" t="s">
+      <c r="J34" s="54" t="s">
         <v>129</v>
       </c>
       <c r="K34" s="26"/>
@@ -2740,44 +2749,44 @@
       <c r="P34" s="26"/>
       <c r="Q34" s="26"/>
       <c r="R34" s="27"/>
-      <c r="S34" s="52" t="s">
+      <c r="S34" s="54" t="s">
         <v>131</v>
       </c>
       <c r="T34" s="26"/>
       <c r="U34" s="27"/>
-      <c r="V34" s="49"/>
+      <c r="V34" s="50"/>
       <c r="W34" s="32" t="s">
         <v>26</v>
       </c>
       <c r="X34" s="26"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="40" t="s">
+      <c r="Z34" s="41" t="s">
         <v>132</v>
       </c>
       <c r="AA34" s="27"/>
-      <c r="AB34" s="40" t="s">
+      <c r="AB34" s="41" t="s">
         <v>133</v>
       </c>
       <c r="AC34" s="26"/>
       <c r="AD34" s="26"/>
       <c r="AE34" s="26"/>
       <c r="AF34" s="27"/>
-      <c r="AG34" s="40" t="s">
+      <c r="AG34" s="41" t="s">
         <v>134</v>
       </c>
       <c r="AH34" s="26"/>
       <c r="AI34" s="27"/>
-      <c r="AJ34" s="47" t="s">
+      <c r="AJ34" s="48" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="35" ht="15.00" customHeight="1">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="53" t="s">
         <v>136</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="27"/>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="54" t="s">
         <v>137</v>
       </c>
       <c r="E35" s="26"/>
@@ -2787,7 +2796,7 @@
         <v>138</v>
       </c>
       <c r="I35" s="27"/>
-      <c r="J35" s="52" t="s">
+      <c r="J35" s="54" t="s">
         <v>139</v>
       </c>
       <c r="K35" s="26"/>
@@ -2800,38 +2809,38 @@
       <c r="P35" s="26"/>
       <c r="Q35" s="26"/>
       <c r="R35" s="27"/>
-      <c r="S35" s="52" t="s">
+      <c r="S35" s="54" t="s">
         <v>141</v>
       </c>
       <c r="T35" s="26"/>
       <c r="U35" s="27"/>
-      <c r="V35" s="49"/>
+      <c r="V35" s="50"/>
       <c r="W35" s="32" t="s">
         <v>27</v>
       </c>
       <c r="X35" s="26"/>
       <c r="Y35" s="27"/>
-      <c r="Z35" s="40"/>
+      <c r="Z35" s="41"/>
       <c r="AA35" s="27"/>
-      <c r="AB35" s="40" t="s">
+      <c r="AB35" s="41" t="s">
         <v>142</v>
       </c>
       <c r="AC35" s="26"/>
       <c r="AD35" s="26"/>
       <c r="AE35" s="26"/>
       <c r="AF35" s="27"/>
-      <c r="AG35" s="40"/>
+      <c r="AG35" s="41"/>
       <c r="AH35" s="26"/>
       <c r="AI35" s="27"/>
-      <c r="AJ35" s="47"/>
+      <c r="AJ35" s="48"/>
     </row>
     <row r="36" ht="15.00" customHeight="1">
-      <c r="A36" s="35" t="s">
+      <c r="A36" s="53" t="s">
         <v>143</v>
       </c>
       <c r="B36" s="26"/>
       <c r="C36" s="27"/>
-      <c r="D36" s="52" t="s">
+      <c r="D36" s="54" t="s">
         <v>144</v>
       </c>
       <c r="E36" s="26"/>
@@ -2841,7 +2850,7 @@
         <v>145</v>
       </c>
       <c r="I36" s="27"/>
-      <c r="J36" s="52" t="s">
+      <c r="J36" s="54" t="s">
         <v>146</v>
       </c>
       <c r="K36" s="26"/>
@@ -2854,36 +2863,36 @@
       <c r="P36" s="26"/>
       <c r="Q36" s="26"/>
       <c r="R36" s="27"/>
-      <c r="S36" s="40"/>
+      <c r="S36" s="41"/>
       <c r="T36" s="26"/>
       <c r="U36" s="27"/>
-      <c r="V36" s="49"/>
+      <c r="V36" s="50"/>
       <c r="W36" s="32" t="s">
         <v>148</v>
       </c>
       <c r="X36" s="26"/>
       <c r="Y36" s="27"/>
-      <c r="Z36" s="40"/>
+      <c r="Z36" s="41"/>
       <c r="AA36" s="27"/>
-      <c r="AB36" s="40" t="s">
+      <c r="AB36" s="41" t="s">
         <v>142</v>
       </c>
       <c r="AC36" s="26"/>
       <c r="AD36" s="26"/>
       <c r="AE36" s="26"/>
       <c r="AF36" s="27"/>
-      <c r="AG36" s="40"/>
+      <c r="AG36" s="41"/>
       <c r="AH36" s="26"/>
       <c r="AI36" s="27"/>
-      <c r="AJ36" s="47"/>
+      <c r="AJ36" s="48"/>
     </row>
     <row r="37" ht="15.00" customHeight="1">
-      <c r="A37" s="35" t="s">
+      <c r="A37" s="53" t="s">
         <v>149</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="27"/>
-      <c r="D37" s="52" t="s">
+      <c r="D37" s="54" t="s">
         <v>150</v>
       </c>
       <c r="E37" s="26"/>
@@ -2893,7 +2902,7 @@
         <v>151</v>
       </c>
       <c r="I37" s="27"/>
-      <c r="J37" s="52" t="s">
+      <c r="J37" s="54" t="s">
         <v>152</v>
       </c>
       <c r="K37" s="26"/>
@@ -2906,226 +2915,226 @@
       <c r="P37" s="26"/>
       <c r="Q37" s="26"/>
       <c r="R37" s="27"/>
-      <c r="S37" s="40" t="s">
+      <c r="S37" s="41" t="s">
         <v>154</v>
       </c>
       <c r="T37" s="26"/>
       <c r="U37" s="27"/>
-      <c r="V37" s="38"/>
+      <c r="V37" s="39"/>
       <c r="W37" s="32" t="s">
         <v>155</v>
       </c>
       <c r="X37" s="26"/>
       <c r="Y37" s="27"/>
-      <c r="Z37" s="40"/>
+      <c r="Z37" s="41"/>
       <c r="AA37" s="27"/>
-      <c r="AB37" s="40" t="s">
+      <c r="AB37" s="41" t="s">
         <v>142</v>
       </c>
       <c r="AC37" s="26"/>
       <c r="AD37" s="26"/>
       <c r="AE37" s="26"/>
       <c r="AF37" s="27"/>
-      <c r="AG37" s="40"/>
+      <c r="AG37" s="41"/>
       <c r="AH37" s="26"/>
       <c r="AI37" s="27"/>
-      <c r="AJ37" s="47"/>
+      <c r="AJ37" s="48"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
       <c r="A38" s="25" t="s">
         <v>156</v>
       </c>
       <c r="B38" s="30"/>
-      <c r="C38" s="55" t="s">
+      <c r="C38" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
       <c r="F38" s="30"/>
-      <c r="G38" s="55" t="s">
+      <c r="G38" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="59"/>
       <c r="K38" s="30"/>
-      <c r="L38" s="55" t="s">
+      <c r="L38" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="M38" s="56"/>
-      <c r="N38" s="56"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="56"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
       <c r="Q38" s="30"/>
-      <c r="R38" s="57" t="s">
+      <c r="R38" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="S38" s="56"/>
-      <c r="T38" s="56"/>
-      <c r="U38" s="56"/>
+      <c r="S38" s="59"/>
+      <c r="T38" s="59"/>
+      <c r="U38" s="59"/>
       <c r="V38" s="30"/>
-      <c r="W38" s="57" t="s">
+      <c r="W38" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="X38" s="56"/>
-      <c r="Y38" s="56"/>
-      <c r="Z38" s="56"/>
-      <c r="AA38" s="56"/>
+      <c r="X38" s="59"/>
+      <c r="Y38" s="59"/>
+      <c r="Z38" s="59"/>
+      <c r="AA38" s="59"/>
       <c r="AB38" s="30"/>
-      <c r="AC38" s="57" t="s">
+      <c r="AC38" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="AD38" s="55" t="s">
+      <c r="AD38" s="58" t="s">
         <v>163</v>
       </c>
-      <c r="AE38" s="56"/>
-      <c r="AF38" s="56"/>
+      <c r="AE38" s="59"/>
+      <c r="AF38" s="59"/>
       <c r="AG38" s="30"/>
-      <c r="AH38" s="55" t="s">
+      <c r="AH38" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="AI38" s="56"/>
+      <c r="AI38" s="59"/>
       <c r="AJ38" s="30"/>
     </row>
     <row r="39" ht="9.00" customHeight="1">
-      <c r="A39" s="58"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="37"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="36"/>
-      <c r="S39" s="59"/>
-      <c r="T39" s="59"/>
-      <c r="U39" s="59"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="59"/>
-      <c r="Y39" s="59"/>
-      <c r="Z39" s="59"/>
-      <c r="AA39" s="59"/>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="38"/>
-      <c r="AD39" s="36"/>
-      <c r="AE39" s="59"/>
-      <c r="AF39" s="59"/>
-      <c r="AG39" s="37"/>
-      <c r="AH39" s="36"/>
-      <c r="AI39" s="59"/>
-      <c r="AJ39" s="37"/>
+      <c r="A39" s="61"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="37"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="37"/>
+      <c r="S39" s="62"/>
+      <c r="T39" s="62"/>
+      <c r="U39" s="62"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="62"/>
+      <c r="Y39" s="62"/>
+      <c r="Z39" s="62"/>
+      <c r="AA39" s="62"/>
+      <c r="AB39" s="38"/>
+      <c r="AC39" s="39"/>
+      <c r="AD39" s="37"/>
+      <c r="AE39" s="62"/>
+      <c r="AF39" s="62"/>
+      <c r="AG39" s="38"/>
+      <c r="AH39" s="37"/>
+      <c r="AI39" s="62"/>
+      <c r="AJ39" s="38"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="63" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61"/>
-      <c r="O40" s="61"/>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="61"/>
-      <c r="S40" s="61"/>
-      <c r="T40" s="61"/>
-      <c r="U40" s="61"/>
-      <c r="V40" s="61"/>
-      <c r="W40" s="61"/>
-      <c r="X40" s="61"/>
-      <c r="Y40" s="61"/>
-      <c r="Z40" s="61"/>
-      <c r="AA40" s="61"/>
-      <c r="AB40" s="61"/>
-      <c r="AC40" s="61"/>
-      <c r="AD40" s="61"/>
-      <c r="AE40" s="61"/>
-      <c r="AF40" s="61"/>
-      <c r="AG40" s="61"/>
-      <c r="AH40" s="61"/>
-      <c r="AI40" s="61"/>
-      <c r="AJ40" s="62"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="64"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="64"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="64"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="64"/>
+      <c r="W40" s="64"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="64"/>
+      <c r="AA40" s="64"/>
+      <c r="AB40" s="64"/>
+      <c r="AC40" s="64"/>
+      <c r="AD40" s="64"/>
+      <c r="AE40" s="64"/>
+      <c r="AF40" s="64"/>
+      <c r="AG40" s="64"/>
+      <c r="AH40" s="64"/>
+      <c r="AI40" s="64"/>
+      <c r="AJ40" s="65"/>
     </row>
     <row r="41" ht="20.25" customHeight="1">
-      <c r="A41" s="63" t="s">
+      <c r="A41" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="B41" s="64"/>
-      <c r="C41" s="65"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="68"/>
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
-      <c r="F41" s="63" t="s">
+      <c r="F41" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="G41" s="64"/>
-      <c r="H41" s="65"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="68"/>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
-      <c r="K41" s="66" t="s">
+      <c r="K41" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="L41" s="63" t="s">
+      <c r="L41" s="66" t="s">
         <v>169</v>
       </c>
-      <c r="M41" s="63" t="s">
+      <c r="M41" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="N41" s="64"/>
-      <c r="O41" s="63"/>
-      <c r="P41" s="63" t="s">
+      <c r="N41" s="67"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="65"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="68"/>
       <c r="S41" s="23"/>
-      <c r="T41" s="67" t="s">
+      <c r="T41" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="U41" s="67" t="s">
+      <c r="U41" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="V41" s="67"/>
-      <c r="W41" s="63" t="s">
+      <c r="V41" s="70"/>
+      <c r="W41" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="X41" s="67"/>
-      <c r="Y41" s="63" t="s">
+      <c r="X41" s="70"/>
+      <c r="Y41" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="Z41" s="64"/>
-      <c r="AA41" s="64"/>
-      <c r="AB41" s="65"/>
+      <c r="Z41" s="67"/>
+      <c r="AA41" s="67"/>
+      <c r="AB41" s="68"/>
       <c r="AC41" s="23"/>
-      <c r="AD41" s="68" t="s">
+      <c r="AD41" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="AE41" s="68"/>
-      <c r="AF41" s="68"/>
-      <c r="AG41" s="63" t="s">
+      <c r="AE41" s="71"/>
+      <c r="AF41" s="71"/>
+      <c r="AG41" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="AH41" s="64"/>
-      <c r="AI41" s="64"/>
-      <c r="AJ41" s="69" t="s">
+      <c r="AH41" s="67"/>
+      <c r="AI41" s="67"/>
+      <c r="AJ41" s="72" t="s">
         <v>175</v>
       </c>
     </row>

--- a/examples/gen_zhixin.xlsx
+++ b/examples/gen_zhixin.xlsx
@@ -574,7 +574,7 @@
   <fonts count="11">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
     </font>
     <font>
       <sz val="14"/>
@@ -882,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1058,6 +1058,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,40 +1073,40 @@
   <dimension ref="A1:AJ41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.75" customWidth="1"/>
-    <col min="2" max="2" width="2.88" customWidth="1"/>
-    <col min="3" max="3" width="6.13" customWidth="1"/>
-    <col min="4" max="4" width="1.00" customWidth="1"/>
-    <col min="5" max="6" width="3.63" customWidth="1"/>
-    <col min="7" max="8" width="5.25" customWidth="1"/>
-    <col min="9" max="9" width="4.25" customWidth="1"/>
-    <col min="10" max="10" width="1.00" customWidth="1"/>
-    <col min="11" max="11" width="5.51" customWidth="1"/>
-    <col min="12" max="12" width="3.25" customWidth="1"/>
-    <col min="13" max="13" width="3.63" customWidth="1"/>
-    <col min="14" max="14" width="1.75" customWidth="1"/>
-    <col min="15" max="15" width="2.51" customWidth="1"/>
-    <col min="16" max="16" width="2.25" customWidth="1"/>
-    <col min="17" max="17" width="3.63" customWidth="1"/>
-    <col min="18" max="18" width="5.51" customWidth="1"/>
-    <col min="19" max="19" width="3.51" customWidth="1"/>
-    <col min="20" max="20" width="8.00" customWidth="1"/>
-    <col min="21" max="21" width="3.38" customWidth="1"/>
-    <col min="22" max="22" width="2.38" customWidth="1"/>
-    <col min="23" max="23" width="4.88" customWidth="1"/>
-    <col min="24" max="25" width="3.25" customWidth="1"/>
-    <col min="26" max="26" width="1.38" customWidth="1"/>
-    <col min="27" max="27" width="3.38" customWidth="1"/>
-    <col min="28" max="28" width="1.51" customWidth="1"/>
-    <col min="29" max="29" width="6.38" customWidth="1"/>
-    <col min="30" max="30" width="5.38" customWidth="1"/>
-    <col min="31" max="31" width="5.63" customWidth="1"/>
-    <col min="32" max="32" width="2.51" customWidth="1"/>
-    <col min="33" max="33" width="4.00" customWidth="1"/>
-    <col min="34" max="34" width="6.38" customWidth="1"/>
-    <col min="35" max="35" width="4.00" customWidth="1"/>
-    <col min="36" max="36" width="8.88" customWidth="1"/>
-    <col min="37" max="16384" width="9.00" customWidth="1"/>
+    <col min="1" max="1" width="2.75" customWidth="1" style="73"/>
+    <col min="2" max="2" width="2.875" customWidth="1" style="73"/>
+    <col min="3" max="3" width="6.125" customWidth="1" style="73"/>
+    <col min="4" max="4" width="1" customWidth="1" hidden="1" style="73"/>
+    <col min="5" max="6" width="3.625" customWidth="1" style="73"/>
+    <col min="7" max="8" width="5.25" customWidth="1" style="73"/>
+    <col min="9" max="9" width="4.25" customWidth="1" style="73"/>
+    <col min="10" max="10" width="1" customWidth="1" style="73"/>
+    <col min="11" max="11" width="5.5083" customWidth="1" style="73"/>
+    <col min="12" max="12" width="3.25" customWidth="1" style="73"/>
+    <col min="13" max="13" width="3.625" customWidth="1" style="73"/>
+    <col min="14" max="14" width="1.75" customWidth="1" style="73"/>
+    <col min="15" max="15" width="2.5083" customWidth="1" style="73"/>
+    <col min="16" max="16" width="2.25" customWidth="1" style="73"/>
+    <col min="17" max="17" width="3.625" customWidth="1" style="73"/>
+    <col min="18" max="18" width="5.5083" customWidth="1" style="73"/>
+    <col min="19" max="19" width="3.5083" customWidth="1" style="73"/>
+    <col min="20" max="20" width="8" customWidth="1" style="73"/>
+    <col min="21" max="21" width="3.375" customWidth="1" style="73"/>
+    <col min="22" max="22" width="2.375" customWidth="1" style="73"/>
+    <col min="23" max="23" width="4.875" customWidth="1" style="73"/>
+    <col min="24" max="25" width="3.25" customWidth="1" style="73"/>
+    <col min="26" max="26" width="1.375" customWidth="1" style="73"/>
+    <col min="27" max="27" width="3.375" customWidth="1" style="73"/>
+    <col min="28" max="28" width="1.5083" customWidth="1" style="73"/>
+    <col min="29" max="29" width="6.375" customWidth="1" style="73"/>
+    <col min="30" max="30" width="5.375" customWidth="1" style="73"/>
+    <col min="31" max="31" width="5.625" customWidth="1" style="73"/>
+    <col min="32" max="32" width="2.5083" customWidth="1" style="73"/>
+    <col min="33" max="33" width="4" customWidth="1" style="73"/>
+    <col min="34" max="34" width="6.375" customWidth="1" style="73"/>
+    <col min="35" max="35" width="4" customWidth="1" style="73"/>
+    <col min="36" max="36" width="8.875" customWidth="1" style="73"/>
+    <col min="37" max="16384" width="9" customWidth="1" style="73"/>
   </cols>
   <sheetData>
     <row r="1" ht="39.00" customHeight="1">
